--- a/jira_export_2026-10-27.xlsx
+++ b/jira_export_2026-10-27.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>56,850 €</t>
+          <t>58,872 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>16,933 €</t>
+          <t>18,955 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -2677,10 +2677,10 @@
         <v>2000</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>638.25</v>
+        <v>1340.325</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>182.36</v>
+        <v>382.95</v>
       </c>
     </row>
     <row r="28">
@@ -3948,8 +3948,8 @@
       <c r="N45" s="12" t="n">
         <v>1100</v>
       </c>
-      <c r="O45" s="16" t="n">
-        <v>0</v>
+      <c r="O45" s="12" t="n">
+        <v>1320</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -12769,10 +12769,10 @@
         <v>70597.86600000001</v>
       </c>
       <c r="O175" s="18" t="n">
-        <v>56849.857</v>
+        <v>58871.932</v>
       </c>
       <c r="P175" s="18" t="n">
-        <v>198.55</v>
+        <v>205.62</v>
       </c>
     </row>
   </sheetData>
@@ -14499,16 +14499,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>470549</v>
+        <v>468527</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>198423</v>
+        <v>197721</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>272126</v>
+        <v>270806</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>216392</v>
+        <v>215072</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14524,16 +14524,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>254588</v>
+        <v>252566</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>68530</v>
+        <v>67828</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>186057</v>
+        <v>184737</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>166846</v>
+        <v>165526</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>

--- a/jira_export_2026-10-27.xlsx
+++ b/jira_export_2026-10-27.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>58,872 €</t>
+          <t>59,277 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>39,706 €</t>
+          <t>40,111 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>453 h</t>
+          <t>459 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="O20" s="15" t="n">
         <v>895</v>
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>353.125</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>353.12</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="22">
@@ -4020,8 +4020,8 @@
       <c r="N46" s="15" t="n">
         <v>810</v>
       </c>
-      <c r="O46" s="16" t="n">
-        <v>405</v>
+      <c r="O46" s="15" t="n">
+        <v>810</v>
       </c>
       <c r="P46" s="15" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -12766,13 +12766,13 @@
       <c r="L175" s="17" t="inlineStr"/>
       <c r="M175" s="17" t="inlineStr"/>
       <c r="N175" s="18" t="n">
-        <v>70597.86600000001</v>
+        <v>69702.86600000001</v>
       </c>
       <c r="O175" s="18" t="n">
-        <v>58871.932</v>
+        <v>59276.932</v>
       </c>
       <c r="P175" s="18" t="n">
-        <v>205.62</v>
+        <v>205.59</v>
       </c>
     </row>
   </sheetData>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>190.25</v>
+        <v>192.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
@@ -14362,7 +14362,7 @@
         <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>224.33</v>
+        <v>226.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>39</v>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>123.83</v>
+        <v>127.33</v>
       </c>
     </row>
   </sheetData>
@@ -14499,16 +14499,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>468527</v>
+        <v>468122</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>197721</v>
+        <v>198972</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>270806</v>
+        <v>269150</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>215072</v>
+        <v>213416</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14527,13 +14527,13 @@
         <v>252566</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>67828</v>
+        <v>69484</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>184737</v>
+        <v>183081</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>165526</v>
+        <v>163870</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -14549,10 +14549,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>212861</v>
+        <v>212456</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>126793</v>
+        <v>126388</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>86068</v>
@@ -14578,7 +14578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14602,7 +14602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 20 commande(s)</t>
+          <t>Épics créées ce mois — 22 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14657,22 +14657,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36614</t>
+          <t>PDMDEP-36645</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36608</t>
+          <t>PDMDEP-36639</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MARSEILLAN</t>
+          <t>Ville de Fleury  Les Aubrais</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00185893</t>
+          <t>00186007</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -14702,22 +14702,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36581</t>
+          <t>PDMDEP-36630</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36572</t>
+          <t>PDMDEP-36621</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE EYMET</t>
+          <t>COMMUNE DE LANGON</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00185751</t>
+          <t>00185979</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -14747,22 +14747,22 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36519</t>
+          <t>PDMDEP-36614</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36510</t>
+          <t>PDMDEP-36608</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LANCON PROVENCE</t>
+          <t>COMMUNE DE MARSEILLAN</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00185247</t>
+          <t>00185893</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
@@ -14792,22 +14792,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36581</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36572</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>MAIRIE EYMET</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -14827,32 +14827,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00185751</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36474</t>
+          <t>PDMDEP-36519</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36465</t>
+          <t>PDMDEP-36510</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE LANCON PROVENCE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14872,32 +14872,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00185032</t>
+          <t>00185247</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>4685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36459</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36453</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE EVREUX </t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -14917,32 +14917,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00184982</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>895</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36474</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36465</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -14962,32 +14962,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00185032</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>985</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36335</t>
+          <t>PDMDEP-36459</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36453</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t xml:space="preserve">COMMUNE DE EVREUX </t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -15007,32 +15007,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00184406</t>
+          <t>00184982</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>500</v>
+        <v>895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -15052,32 +15052,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1800</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36349</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36345</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LEUCATE Service Achat</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -15097,32 +15097,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00184482</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36387</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36381</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRIANCON</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -15142,32 +15142,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00184667</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36376</t>
+          <t>PDMDEP-36349</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36370</t>
+          <t>PDMDEP-36345</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>MAIRIE DE LEUCATE Service Achat</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -15187,42 +15187,42 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00184665</t>
+          <t>00184482</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36387</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36381</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE DE BRIANCON</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -15232,37 +15232,37 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00184667</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36427</t>
+          <t>PDMDEP-36376</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -15277,32 +15277,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00184846</t>
+          <t>00184665</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>3575</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36428</t>
+          <t>PDMDEP-36197</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36190</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -15322,22 +15322,22 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00184334</t>
+          <t>00183894</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>0</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36439</t>
+          <t>PDMDEP-36428</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36435</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANGERS</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -15367,32 +15367,32 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00184863</t>
+          <t>00184334</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36497</t>
+          <t>PDMDEP-36427</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36493</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE SEINE ET MARNE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00185186</t>
+          <t>00184846</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>500</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36555</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36549</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -15457,32 +15457,32 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00185556</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>750</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36402</t>
+          <t>PDMDEP-36497</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36398</t>
+          <t>PDMDEP-36493</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+          <t>DEPARTEMENT DE SEINE ET MARNE</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -15502,104 +15502,152 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>00184748</t>
+          <t>00185186</t>
         </is>
       </c>
       <c r="I23" s="25" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36555</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36549</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>00185556</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36402</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36398</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>00184748</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I26" s="26" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>20 commande(s)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>28468</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>8 commande(s)</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>16853</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" s="17" t="n"/>
@@ -15610,10 +15658,52 @@
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>12 commande(s)</t>
+          <t>22 commande(s)</t>
         </is>
       </c>
       <c r="I27" s="24" t="n">
+        <v>28468</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>16853</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>14 commande(s)</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="n">
         <v>11615</v>
       </c>
     </row>

--- a/jira_export_2026-10-27.xlsx
+++ b/jira_export_2026-10-27.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>59,277 €</t>
+          <t>60,129 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>18,955 €</t>
+          <t>19,807 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4092,11 +4092,11 @@
       <c r="N47" s="12" t="n">
         <v>480</v>
       </c>
-      <c r="O47" s="16" t="n">
-        <v>0</v>
+      <c r="O47" s="12" t="n">
+        <v>552</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48">
@@ -7678,32 +7678,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7713,69 +7713,69 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>450</v>
+        <v>910</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7785,64 +7785,64 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>910</v>
+        <v>4050</v>
       </c>
       <c r="O99" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
@@ -7873,16 +7873,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>4050</v>
+        <v>1050</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7894,27 +7894,27 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7945,16 +7945,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1050</v>
+        <v>433.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7966,32 +7966,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8001,34 +8001,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8038,12 +8038,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8110,12 +8110,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
@@ -8161,16 +8161,16 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8182,32 +8182,32 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -8217,34 +8217,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8254,12 +8254,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8294,27 +8294,27 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8326,27 +8326,27 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
@@ -8377,16 +8377,16 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8398,12 +8398,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
@@ -8470,12 +8470,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -8510,27 +8510,27 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="O109" s="16" t="n">
         <v>0</v>
@@ -8542,32 +8542,32 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -8577,32 +8577,32 @@
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="O110" s="16" t="n">
         <v>0</v>
@@ -8614,32 +8614,32 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -8649,69 +8649,69 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>255</v>
-      </c>
-      <c r="O111" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
+        <v>175</v>
       </c>
       <c r="P111" s="12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -8721,34 +8721,34 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8758,27 +8758,27 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -8798,29 +8798,29 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.5</v>
+        <v>10.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8830,12 +8830,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8845,13 +8845,11 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v/>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8870,44 +8868,44 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8917,12 +8915,12 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8937,34 +8935,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.75</v>
+        <v>1.9</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O115" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8974,27 +8972,27 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
@@ -9009,28 +9007,28 @@
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>10.25</v>
+        <v>1.9</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9046,12 +9044,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9061,11 +9059,13 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9079,38 +9079,38 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
-        <v>0</v>
+        <v>1290</v>
+      </c>
+      <c r="O117" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P117" s="12" t="n">
-        <v>0</v>
+        <v>471.05</v>
       </c>
     </row>
     <row r="118">
@@ -9167,18 +9167,18 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>275</v>
-      </c>
-      <c r="O118" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9260,12 +9260,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9275,13 +9275,11 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v/>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9300,44 +9298,44 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>1290</v>
+        <v>1000</v>
       </c>
       <c r="O120" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>471.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9347,13 +9345,11 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v/>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9367,34 +9363,34 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O121" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9404,27 +9400,27 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Déploiement LiEx</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -9444,23 +9440,23 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9476,26 +9472,28 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -9514,29 +9512,29 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>4.5</v>
+        <v>0.75</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O123" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9546,22 +9544,22 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9584,60 +9582,58 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>460</v>
+        <v>3016.08</v>
       </c>
       <c r="O124" s="16" t="n">
-        <v>0</v>
+        <v>2178.28</v>
       </c>
       <c r="P124" s="15" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE DRANCY</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v/>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9651,28 +9647,28 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9688,28 +9684,26 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v/>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -9728,54 +9722,54 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.75</v>
+        <v>11.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0</v>
+        <v>2497.125</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>0</v>
+        <v>217.14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9793,59 +9787,59 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O127" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9863,28 +9857,28 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
@@ -9900,12 +9894,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9915,7 +9909,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9938,44 +9932,44 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="12" t="n">
-        <v>2497.125</v>
+        <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
-        <v>217.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9985,7 +9979,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10008,7 +10002,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
@@ -10019,12 +10013,12 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10089,12 +10083,12 @@
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10110,22 +10104,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10138,35 +10132,27 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30080</t>
-        </is>
-      </c>
-      <c r="M132" s="14" t="inlineStr">
-        <is>
-          <t>00152635</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10180,22 +10166,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10213,28 +10199,28 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10250,22 +10236,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10288,23 +10274,23 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
@@ -10320,22 +10306,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22120</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD 29 ] FLUX WFS</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10348,7 +10334,7 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
@@ -10358,17 +10344,25 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr"/>
-      <c r="M135" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10382,22 +10376,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10410,35 +10404,23 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr"/>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M136" s="14" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10452,22 +10434,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10490,23 +10472,23 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
@@ -10522,22 +10504,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10560,29 +10542,29 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N138" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="O138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="15" t="n">
@@ -10592,22 +10574,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10620,23 +10602,35 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10650,26 +10644,28 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
@@ -10678,35 +10674,27 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10720,22 +10708,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10748,7 +10736,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -10758,25 +10746,17 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M141" s="11" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10790,22 +10770,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10818,7 +10798,7 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
@@ -10828,25 +10808,17 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10860,61 +10832,67 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v/>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O143" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10924,22 +10902,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10952,7 +10930,7 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
@@ -10962,17 +10940,25 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10986,22 +10972,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11019,19 +11005,19 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11048,22 +11034,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11071,44 +11057,36 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M146" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
       <c r="N146" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="15" t="n">
@@ -11118,12 +11096,12 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
@@ -11133,7 +11111,7 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11146,7 +11124,7 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -11156,25 +11134,17 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M147" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
@@ -11188,22 +11158,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11226,14 +11196,14 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11250,22 +11220,22 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11283,19 +11253,19 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11312,12 +11282,12 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
@@ -11327,7 +11297,7 @@
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11340,7 +11310,7 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr">
@@ -11350,17 +11320,25 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr"/>
-      <c r="M150" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M150" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N150" s="15" t="n">
         <v>0</v>
       </c>
@@ -11374,22 +11352,22 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11405,21 +11383,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H151" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11436,22 +11410,22 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11474,17 +11448,25 @@
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr"/>
-      <c r="M152" s="14" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11498,12 +11480,12 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
@@ -11513,7 +11495,7 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11529,30 +11511,26 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H153" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M153" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N153" s="12" t="n">
@@ -11568,26 +11546,24 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C154" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
-        </is>
-      </c>
-      <c r="E154" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F154" s="14" t="inlineStr">
         <is>
@@ -11599,17 +11575,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H154" s="14" t="inlineStr"/>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="L154" s="14" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -11626,27 +11606,21 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C155" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E155" s="11" t="n">
-        <v/>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr"/>
       <c r="F155" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11654,35 +11628,23 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H155" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
@@ -11696,32 +11658,18 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C156" s="14" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D156" s="14" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F156" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr"/>
+      <c r="D156" s="14" t="inlineStr"/>
+      <c r="E156" s="14" t="inlineStr"/>
+      <c r="F156" s="14" t="inlineStr"/>
       <c r="G156" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
@@ -11730,30 +11678,26 @@
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M156" s="14" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr"/>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="15" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P156" s="15" t="n">
         <v>0</v>
@@ -11762,25 +11706,21 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr"/>
       <c r="F157" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11788,24 +11728,20 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H157" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="L157" s="11" t="inlineStr"/>
       <c r="M157" s="11" t="inlineStr"/>
@@ -11822,18 +11758,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11850,11 +11786,11 @@
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" s="14" t="n">
         <v>0.25</v>
@@ -11874,18 +11810,26 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="11" t="inlineStr"/>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
       <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr"/>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
@@ -11894,46 +11838,50 @@
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
-      <c r="M159" s="11" t="inlineStr"/>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N159" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" s="12" t="n">
-        <v>210.8</v>
+        <v>450</v>
+      </c>
+      <c r="O159" s="16" t="n">
+        <v>350</v>
       </c>
       <c r="P159" s="12" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11950,11 +11898,11 @@
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K160" s="14" t="n">
         <v>0.25</v>
@@ -11974,18 +11922,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11996,23 +11944,31 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K161" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr"/>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N161" s="12" t="n">
         <v>0</v>
       </c>
@@ -12026,18 +11982,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12048,56 +12004,48 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L162" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M162" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
       <c r="N162" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O162" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="O162" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P162" s="15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12114,14 +12062,14 @@
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L163" s="11" t="inlineStr"/>
       <c r="M163" s="11" t="inlineStr"/>
@@ -12138,18 +12086,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12160,31 +12108,23 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M164" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L164" s="14" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12198,18 +12138,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12220,23 +12160,31 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12250,18 +12198,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12272,23 +12220,31 @@
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L166" s="14" t="inlineStr"/>
-      <c r="M166" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L166" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M166" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N166" s="15" t="n">
         <v>0</v>
       </c>
@@ -12302,18 +12258,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12330,14 +12286,14 @@
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="L167" s="11" t="inlineStr"/>
       <c r="M167" s="11" t="inlineStr"/>
@@ -12354,18 +12310,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12382,23 +12338,23 @@
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34335</t>
+          <t>PDMDEP-30236</t>
         </is>
       </c>
       <c r="M168" s="14" t="inlineStr">
         <is>
-          <t>00168072</t>
+          <t>00152992</t>
         </is>
       </c>
       <c r="N168" s="15" t="n">
@@ -12414,18 +12370,18 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12436,31 +12392,23 @@
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L169" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L169" s="11" t="inlineStr"/>
+      <c r="M169" s="11" t="inlineStr"/>
       <c r="N169" s="12" t="n">
         <v>0</v>
       </c>
@@ -12474,18 +12422,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12496,23 +12444,31 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr"/>
-      <c r="M170" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
       <c r="N170" s="15" t="n">
         <v>0</v>
       </c>
@@ -12526,18 +12482,18 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12548,31 +12504,23 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L171" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L171" s="11" t="inlineStr"/>
+      <c r="M171" s="11" t="inlineStr"/>
       <c r="N171" s="12" t="n">
         <v>0</v>
       </c>
@@ -12584,195 +12532,31 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="13" t="inlineStr">
-        <is>
-          <t>PSC-1060</t>
-        </is>
-      </c>
-      <c r="B172" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="C172" s="14" t="inlineStr"/>
-      <c r="D172" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="E172" s="14" t="inlineStr"/>
-      <c r="F172" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G172" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H172" s="14" t="inlineStr"/>
-      <c r="I172" s="14" t="inlineStr">
-        <is>
-          <t>12/11/2025</t>
-        </is>
-      </c>
-      <c r="J172" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K172" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L172" s="14" t="inlineStr"/>
-      <c r="M172" s="14" t="inlineStr"/>
-      <c r="N172" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O172" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1047</t>
-        </is>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C173" s="11" t="inlineStr"/>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="inlineStr"/>
-      <c r="F173" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G173" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H173" s="11" t="inlineStr"/>
-      <c r="I173" s="11" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="J173" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K173" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L173" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
-      <c r="N173" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O173" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P173" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="13" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B174" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C174" s="14" t="inlineStr"/>
-      <c r="D174" s="14" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E174" s="14" t="inlineStr"/>
-      <c r="F174" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G174" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H174" s="14" t="inlineStr"/>
-      <c r="I174" s="14" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J174" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K174" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L174" s="14" t="inlineStr"/>
-      <c r="M174" s="14" t="inlineStr"/>
-      <c r="N174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="17" t="inlineStr">
+      <c r="A172" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B175" s="17" t="inlineStr"/>
-      <c r="C175" s="17" t="inlineStr"/>
-      <c r="D175" s="17" t="inlineStr"/>
-      <c r="E175" s="17" t="inlineStr"/>
-      <c r="F175" s="17" t="inlineStr"/>
-      <c r="G175" s="17" t="inlineStr"/>
-      <c r="H175" s="17" t="inlineStr"/>
-      <c r="I175" s="17" t="inlineStr"/>
-      <c r="J175" s="17" t="inlineStr"/>
-      <c r="K175" s="17" t="inlineStr"/>
-      <c r="L175" s="17" t="inlineStr"/>
-      <c r="M175" s="17" t="inlineStr"/>
-      <c r="N175" s="18" t="n">
-        <v>69702.86600000001</v>
-      </c>
-      <c r="O175" s="18" t="n">
-        <v>59276.932</v>
-      </c>
-      <c r="P175" s="18" t="n">
-        <v>205.59</v>
+      <c r="B172" s="17" t="inlineStr"/>
+      <c r="C172" s="17" t="inlineStr"/>
+      <c r="D172" s="17" t="inlineStr"/>
+      <c r="E172" s="17" t="inlineStr"/>
+      <c r="F172" s="17" t="inlineStr"/>
+      <c r="G172" s="17" t="inlineStr"/>
+      <c r="H172" s="17" t="inlineStr"/>
+      <c r="I172" s="17" t="inlineStr"/>
+      <c r="J172" s="17" t="inlineStr"/>
+      <c r="K172" s="17" t="inlineStr"/>
+      <c r="L172" s="17" t="inlineStr"/>
+      <c r="M172" s="17" t="inlineStr"/>
+      <c r="N172" s="18" t="n">
+        <v>68462.86600000001</v>
+      </c>
+      <c r="O172" s="18" t="n">
+        <v>60128.932</v>
+      </c>
+      <c r="P172" s="18" t="n">
+        <v>208.55</v>
       </c>
     </row>
   </sheetData>
@@ -12945,9 +12729,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14499,16 +14280,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>468122</v>
+        <v>467270</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>198972</v>
+        <v>198672</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>269150</v>
+        <v>268598</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>213416</v>
+        <v>212864</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14524,16 +14305,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>252566</v>
+        <v>251714</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69484</v>
+        <v>69184</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>183081</v>
+        <v>182529</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>163870</v>
+        <v>163318</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>

--- a/jira_export_2026-10-27.xlsx
+++ b/jira_export_2026-10-27.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>60,129 €</t>
+          <t>61,055 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>40,111 €</t>
+          <t>41,037 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>459 h</t>
+          <t>471 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -948,7 +948,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>500</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="L25" s="11" t="inlineStr"/>
       <c r="M25" s="11" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>926.4</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>926.4</v>
+        <v>1852.8</v>
       </c>
       <c r="P28" s="15" t="n">
         <v>0</v>
@@ -4822,12 +4822,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4862,29 +4862,29 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4894,27 +4894,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4934,21 +4934,29 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="O59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4958,27 +4966,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -4988,7 +4996,7 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H60" s="14" t="inlineStr">
@@ -5005,22 +5013,14 @@
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M60" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>8.75</v>
+      </c>
+      <c r="L60" s="14" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
       <c r="N60" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5030,32 +5030,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5065,69 +5065,69 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1440</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>1512</v>
+        <v>2500</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>70.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5137,49 +5137,49 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>175</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>0</v>
+        <v>1440</v>
+      </c>
+      <c r="O62" s="15" t="n">
+        <v>1512</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5221,67 +5221,67 @@
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>775.6</v>
+        <v>175</v>
       </c>
       <c r="O63" s="16" t="n">
-        <v>692.5</v>
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
-        <v>230.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
@@ -5293,87 +5293,87 @@
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
-        <v>0</v>
+        <v>775.6</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>692.5</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>0</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="12" t="n">
-        <v>5388.936</v>
-      </c>
-      <c r="O65" s="16" t="n">
-        <v>4811.55</v>
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
@@ -5382,27 +5382,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5433,19 +5433,19 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>4811.55</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5454,27 +5454,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5505,19 +5505,19 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="O67" s="16" t="n">
-        <v>840</v>
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
@@ -5526,27 +5526,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5561,64 +5561,64 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>1786.1</v>
+        <v>1700</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>909.9</v>
+        <v>840</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5638,64 +5638,64 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>170</v>
+        <v>1786.1</v>
       </c>
       <c r="O69" s="16" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5705,64 +5705,64 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>1242.9</v>
+        <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>58.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5789,57 +5789,57 @@
         <v>4</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4.5</v>
+        <v>21.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>484</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>572</v>
+        <v>3000</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>1242.9</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>127.11</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5849,64 +5849,64 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="O72" s="16" t="n">
-        <v>0</v>
+        <v>484</v>
+      </c>
+      <c r="O72" s="15" t="n">
+        <v>572</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>0</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5937,16 +5937,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5958,32 +5958,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -5993,34 +5993,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6030,27 +6030,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6070,44 +6070,44 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>8.25</v>
+        <v>0.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>465.85</v>
+        <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6142,59 +6142,59 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>3.5</v>
+        <v>8.25</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>0</v>
+        <v>465.85</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>0</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6221,16 +6221,16 @@
         <v>4</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6246,32 +6246,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6286,29 +6286,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6318,27 +6318,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6353,35 +6353,35 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O79" s="16" t="n">
-        <v>1062</v>
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6390,27 +6390,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6441,19 +6441,19 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="P80" s="15" t="n">
         <v>0</v>
@@ -6462,27 +6462,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6513,19 +6513,19 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>3547.9</v>
-      </c>
-      <c r="O81" s="12" t="n">
-        <v>3547.9</v>
+        <v>203.5</v>
+      </c>
+      <c r="O81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
@@ -6534,27 +6534,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>3547.9</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>3547.9</v>
       </c>
       <c r="P82" s="15" t="n">
         <v>0</v>
@@ -6606,32 +6606,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6646,59 +6646,59 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
-        <v>112.38</v>
+        <v>500</v>
+      </c>
+      <c r="O83" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -6718,61 +6718,69 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr"/>
-      <c r="M84" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33315</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>00167138</t>
+        </is>
+      </c>
       <c r="N84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0</v>
+        <v>112.38</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6782,29 +6790,21 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M85" s="11" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
       <c r="N85" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6814,27 +6814,27 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
@@ -6865,16 +6865,16 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O86" s="16" t="n">
         <v>0</v>
@@ -8182,27 +8182,27 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
@@ -8233,16 +8233,16 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>203.5</v>
+        <v>130</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8254,32 +8254,32 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -8289,34 +8289,34 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8326,32 +8326,32 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8361,32 +8361,32 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8398,32 +8398,32 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -8433,69 +8433,69 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O108" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
+        <v>175</v>
       </c>
       <c r="P108" s="15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -8505,34 +8505,34 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="O109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8542,27 +8542,27 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
@@ -8582,29 +8582,29 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1.5</v>
+        <v>10.25</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8614,12 +8614,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8629,13 +8629,11 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -8654,44 +8652,44 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="12" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8701,12 +8699,12 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
@@ -8721,34 +8719,34 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.75</v>
+        <v>1.9</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8758,27 +8756,27 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -8793,28 +8791,28 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>10.25</v>
+        <v>1.9</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8830,12 +8828,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8845,11 +8843,13 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8863,38 +8863,38 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
-        <v>0</v>
+        <v>1290</v>
+      </c>
+      <c r="O114" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P114" s="15" t="n">
-        <v>0</v>
+        <v>471.05</v>
       </c>
     </row>
     <row r="115">
@@ -8951,18 +8951,18 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>275</v>
-      </c>
-      <c r="O115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9044,12 +9044,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9059,13 +9059,11 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9084,44 +9082,44 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>1290</v>
+        <v>1000</v>
       </c>
       <c r="O117" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
-        <v>471.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9131,13 +9129,11 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v/>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -9151,34 +9147,34 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="15" t="n">
+        <v>460</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9188,27 +9184,27 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Déploiement LiEx</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -9228,23 +9224,23 @@
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9260,26 +9256,28 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9298,29 +9296,29 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>4.5</v>
+        <v>0.75</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9330,22 +9328,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9368,60 +9366,58 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>460</v>
+        <v>3016.08</v>
       </c>
       <c r="O121" s="16" t="n">
-        <v>0</v>
+        <v>2178.28</v>
       </c>
       <c r="P121" s="12" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE DRANCY</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v/>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
@@ -9435,28 +9431,28 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9472,28 +9468,26 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v/>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -9512,54 +9506,54 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.75</v>
+        <v>11.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O123" s="12" t="n">
-        <v>0</v>
+        <v>2497.125</v>
       </c>
       <c r="P123" s="12" t="n">
-        <v>0</v>
+        <v>217.14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9577,59 +9571,59 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O124" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9647,28 +9641,28 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9684,12 +9678,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9699,7 +9693,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9722,44 +9716,44 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>2497.125</v>
+        <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>217.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9769,7 +9763,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9792,7 +9786,7 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
@@ -9803,12 +9797,12 @@
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9873,12 +9867,12 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
@@ -9894,22 +9888,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9922,35 +9916,27 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30080</t>
-        </is>
-      </c>
-      <c r="M129" s="11" t="inlineStr">
-        <is>
-          <t>00152635</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
@@ -9964,22 +9950,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9997,28 +9983,28 @@
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10034,22 +10020,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10072,23 +10058,23 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10104,22 +10090,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22120</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD 29 ] FLUX WFS</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10132,7 +10118,7 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
@@ -10142,17 +10128,25 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10166,22 +10160,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10194,35 +10188,23 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H133" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M133" s="11" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="12" t="n">
         <v>0</v>
       </c>
@@ -10236,22 +10218,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10274,23 +10256,23 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
@@ -10306,22 +10288,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10344,23 +10326,23 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
@@ -10376,22 +10358,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10404,23 +10386,35 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10434,26 +10428,28 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -10462,35 +10458,27 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10504,22 +10492,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10532,7 +10520,7 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
@@ -10542,25 +10530,17 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L138" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M138" s="14" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
       <c r="N138" s="15" t="n">
         <v>0</v>
       </c>
@@ -10574,22 +10554,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10602,7 +10582,7 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -10612,25 +10592,17 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M139" s="11" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10644,61 +10616,67 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="n">
+        <v/>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="15" t="n">
@@ -10708,22 +10686,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10736,7 +10714,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -10746,17 +10724,25 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
-      <c r="M141" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10770,22 +10756,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10803,19 +10789,19 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L142" s="14" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -10832,22 +10818,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10855,44 +10841,36 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10902,12 +10880,12 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -10917,7 +10895,7 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10930,7 +10908,7 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
@@ -10940,25 +10918,17 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M144" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10972,22 +10942,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11010,14 +10980,14 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11034,22 +11004,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11067,19 +11037,19 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11096,12 +11066,12 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
@@ -11111,7 +11081,7 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11124,7 +11094,7 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -11134,17 +11104,25 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr"/>
-      <c r="M147" s="11" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
@@ -11158,22 +11136,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11189,21 +11167,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H148" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H148" s="14" t="inlineStr"/>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11220,22 +11194,22 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11258,17 +11232,25 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr"/>
-      <c r="M149" s="11" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N149" s="12" t="n">
         <v>0</v>
       </c>
@@ -11282,12 +11264,12 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
@@ -11297,7 +11279,7 @@
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11313,30 +11295,26 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H150" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M150" s="14" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N150" s="15" t="n">
@@ -11352,26 +11330,24 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
@@ -11383,17 +11359,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H151" s="11" t="inlineStr"/>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11410,27 +11390,21 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C152" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E152" s="14" t="n">
-        <v/>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr"/>
       <c r="F152" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11438,35 +11412,23 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H152" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M152" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11480,32 +11442,18 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E153" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F153" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr"/>
+      <c r="D153" s="11" t="inlineStr"/>
+      <c r="E153" s="11" t="inlineStr"/>
+      <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
@@ -11514,30 +11462,26 @@
       <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="12" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P153" s="12" t="n">
         <v>0</v>
@@ -11546,25 +11490,21 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E154" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>COMMUNE DE VALENCAY</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr"/>
       <c r="F154" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11572,24 +11512,20 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H154" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="L154" s="14" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -11606,18 +11542,18 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr"/>
@@ -11634,11 +11570,11 @@
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" s="11" t="n">
         <v>0.25</v>
@@ -11658,18 +11594,26 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr"/>
-      <c r="D156" s="14" t="inlineStr"/>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
       <c r="E156" s="14" t="inlineStr"/>
-      <c r="F156" s="14" t="inlineStr"/>
+      <c r="F156" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
@@ -11678,46 +11622,50 @@
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
-      <c r="M156" s="14" t="inlineStr"/>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N156" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" s="15" t="n">
-        <v>210.8</v>
+        <v>450</v>
+      </c>
+      <c r="O156" s="16" t="n">
+        <v>350</v>
       </c>
       <c r="P156" s="15" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr"/>
@@ -11734,11 +11682,11 @@
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K157" s="11" t="n">
         <v>0.25</v>
@@ -11758,18 +11706,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11780,23 +11728,31 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K158" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L158" s="14" t="inlineStr"/>
-      <c r="M158" s="14" t="inlineStr"/>
+      <c r="L158" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M158" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N158" s="15" t="n">
         <v>0</v>
       </c>
@@ -11810,18 +11766,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11832,56 +11788,48 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M159" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr"/>
+      <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O159" s="16" t="n">
-        <v>350</v>
+        <v>0</v>
+      </c>
+      <c r="O159" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P159" s="12" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11898,14 +11846,14 @@
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L160" s="14" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -11922,18 +11870,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11944,31 +11892,23 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M161" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L161" s="11" t="inlineStr"/>
+      <c r="M161" s="11" t="inlineStr"/>
       <c r="N161" s="12" t="n">
         <v>0</v>
       </c>
@@ -11982,18 +11922,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12004,23 +11944,31 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L162" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M162" s="14" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N162" s="15" t="n">
         <v>0</v>
       </c>
@@ -12034,18 +11982,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12056,23 +12004,31 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N163" s="12" t="n">
         <v>0</v>
       </c>
@@ -12086,18 +12042,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12114,14 +12070,14 @@
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="L164" s="14" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -12138,18 +12094,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12166,23 +12122,23 @@
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34335</t>
+          <t>PDMDEP-30236</t>
         </is>
       </c>
       <c r="M165" s="11" t="inlineStr">
         <is>
-          <t>00168072</t>
+          <t>00152992</t>
         </is>
       </c>
       <c r="N165" s="12" t="n">
@@ -12198,18 +12154,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12220,31 +12176,23 @@
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L166" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M166" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L166" s="14" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
       <c r="N166" s="15" t="n">
         <v>0</v>
       </c>
@@ -12258,18 +12206,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12280,23 +12228,31 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L167" s="11" t="inlineStr"/>
-      <c r="M167" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L167" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
       <c r="N167" s="12" t="n">
         <v>0</v>
       </c>
@@ -12310,18 +12266,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12332,31 +12288,23 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L168" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M168" s="14" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L168" s="14" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
       <c r="N168" s="15" t="n">
         <v>0</v>
       </c>
@@ -12368,195 +12316,31 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1060</t>
-        </is>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="C169" s="11" t="inlineStr"/>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE DE COUBLEVIE</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr"/>
-      <c r="F169" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G169" s="11" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H169" s="11" t="inlineStr"/>
-      <c r="I169" s="11" t="inlineStr">
-        <is>
-          <t>12/11/2025</t>
-        </is>
-      </c>
-      <c r="J169" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K169" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L169" s="11" t="inlineStr"/>
-      <c r="M169" s="11" t="inlineStr"/>
-      <c r="N169" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O169" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>PSC-1047</t>
-        </is>
-      </c>
-      <c r="B170" s="14" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C170" s="14" t="inlineStr"/>
-      <c r="D170" s="14" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E170" s="14" t="inlineStr"/>
-      <c r="F170" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G170" s="14" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H170" s="14" t="inlineStr"/>
-      <c r="I170" s="14" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="J170" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K170" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M170" s="14" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
-      <c r="N170" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="10" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C171" s="11" t="inlineStr"/>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E171" s="11" t="inlineStr"/>
-      <c r="F171" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G171" s="11" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H171" s="11" t="inlineStr"/>
-      <c r="I171" s="11" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J171" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K171" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L171" s="11" t="inlineStr"/>
-      <c r="M171" s="11" t="inlineStr"/>
-      <c r="N171" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O171" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="17" t="inlineStr">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B172" s="17" t="inlineStr"/>
-      <c r="C172" s="17" t="inlineStr"/>
-      <c r="D172" s="17" t="inlineStr"/>
-      <c r="E172" s="17" t="inlineStr"/>
-      <c r="F172" s="17" t="inlineStr"/>
-      <c r="G172" s="17" t="inlineStr"/>
-      <c r="H172" s="17" t="inlineStr"/>
-      <c r="I172" s="17" t="inlineStr"/>
-      <c r="J172" s="17" t="inlineStr"/>
-      <c r="K172" s="17" t="inlineStr"/>
-      <c r="L172" s="17" t="inlineStr"/>
-      <c r="M172" s="17" t="inlineStr"/>
-      <c r="N172" s="18" t="n">
-        <v>68462.86600000001</v>
-      </c>
-      <c r="O172" s="18" t="n">
-        <v>60128.932</v>
-      </c>
-      <c r="P172" s="18" t="n">
-        <v>208.55</v>
+      <c r="B169" s="17" t="inlineStr"/>
+      <c r="C169" s="17" t="inlineStr"/>
+      <c r="D169" s="17" t="inlineStr"/>
+      <c r="E169" s="17" t="inlineStr"/>
+      <c r="F169" s="17" t="inlineStr"/>
+      <c r="G169" s="17" t="inlineStr"/>
+      <c r="H169" s="17" t="inlineStr"/>
+      <c r="I169" s="17" t="inlineStr"/>
+      <c r="J169" s="17" t="inlineStr"/>
+      <c r="K169" s="17" t="inlineStr"/>
+      <c r="L169" s="17" t="inlineStr"/>
+      <c r="M169" s="17" t="inlineStr"/>
+      <c r="N169" s="18" t="n">
+        <v>67630.36600000001</v>
+      </c>
+      <c r="O169" s="18" t="n">
+        <v>61055.33200000001</v>
+      </c>
+      <c r="P169" s="18" t="n">
+        <v>203.13</v>
       </c>
     </row>
   </sheetData>
@@ -12726,9 +12510,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14134,7 +13915,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>192.25</v>
+        <v>192.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
@@ -14143,7 +13924,7 @@
         <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>226.33</v>
+        <v>226.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>39</v>
@@ -14153,7 +13934,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
     </row>
@@ -14164,16 +13945,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>45.25</v>
+        <v>54.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>16.75</v>
+        <v>19.75</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -14183,7 +13964,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
     </row>
@@ -14195,7 +13976,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>127.33</v>
+        <v>127.58</v>
       </c>
     </row>
   </sheetData>
@@ -14280,10 +14061,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>467270</v>
+        <v>466343</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>198672</v>
+        <v>197746</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>268598</v>
@@ -14330,10 +14111,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>212456</v>
+        <v>211530</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>126388</v>
+        <v>125462</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>86068</v>

--- a/jira_export_2026-10-27.xlsx
+++ b/jira_export_2026-10-27.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>61,055 €</t>
+          <t>61,612 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>41,037 €</t>
+          <t>41,594 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>471 h</t>
+          <t>473 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>1340.325</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>382.95</v>
+        <v>243.7</v>
       </c>
     </row>
     <row r="28">
@@ -4885,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0</v>
+        <v>556.5</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="59">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -12337,10 +12337,10 @@
         <v>67630.36600000001</v>
       </c>
       <c r="O169" s="18" t="n">
-        <v>61055.33200000001</v>
+        <v>61611.83200000001</v>
       </c>
       <c r="P169" s="18" t="n">
-        <v>203.13</v>
+        <v>203.63</v>
       </c>
     </row>
   </sheetData>
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>192.5</v>
+        <v>194.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
@@ -13924,7 +13924,7 @@
         <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>226.58</v>
+        <v>228.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>39</v>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -14061,10 +14061,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>466343</v>
+        <v>465787</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>197746</v>
+        <v>197189</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>268598</v>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>211530</v>
+        <v>210973</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>125462</v>
+        <v>124905</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>86068</v>
